--- a/verification/cases/roundtrip/formulas_statistical/init.xlsx
+++ b/verification/cases/roundtrip/formulas_statistical/init.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/statistical/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0346FD-3E56-F64A-8A7A-5000F66CCD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C49B4CB-6502-49CE-A46B-5CE7D623C97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="660" windowWidth="29480" windowHeight="17920" xr2:uid="{2A17A059-3A2D-D044-9340-8F7C314EEA32}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2A17A059-3A2D-D044-9340-8F7C314EEA32}"/>
   </bookViews>
   <sheets>
     <sheet name="Statistical Functions" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -899,7 +899,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -922,20 +922,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60BD2570-6520-A945-BE02-CA775A5C6696}">
   <dimension ref="B2:K159"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="42.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -949,7 +949,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -960,7 +960,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
@@ -974,7 +974,7 @@
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>1E-100</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>5.0000000000000001E-100</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
         <v>16</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>9.9999999999999998E-201</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>17</v>
       </c>
@@ -1126,7 +1126,7 @@
         <v>4.9999999999999999E-200</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>18</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>9.9999999999999991E-308</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>19</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>5.0000000000000001E-307</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="5" t="s">
         <v>21</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="10" t="s">
         <v>22</v>
       </c>
@@ -1228,7 +1228,7 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -1240,7 +1240,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>23</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="5" t="s">
         <v>24</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>8.5714285714285714E-101</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="5" t="s">
         <v>25</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="5" t="s">
         <v>26</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="5" t="s">
         <v>27</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
         <v>28</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
         <v>29</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>5.0000000000000001E-100</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="5" t="s">
         <v>30</v>
       </c>
@@ -1559,7 +1559,7 @@
         <v>9.9999999999999998E-201</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="5" t="s">
         <v>31</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="5" t="s">
         <v>32</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>1.864454471471609E-100</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="5" t="s">
         <v>33</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>3.4761904761904767E-200</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="10" t="s">
         <v>34</v>
       </c>
@@ -1696,7 +1696,7 @@
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1708,7 +1708,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
         <v>35</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="5">
         <v>0</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="5">
         <v>0.1</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>6.0000000000000004E-308</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="5">
         <v>0.25</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>2.9999999999999999E-307</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="5">
         <v>0.5</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>9.9999999999999998E-201</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="5">
         <v>0.75</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>5.0000000000000001E-101</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="5">
         <v>0.9</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>2.6000000000000014E-100</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="5">
         <v>1</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>5.0000000000000001E-100</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>36</v>
       </c>
@@ -2041,7 +2041,7 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -2053,7 +2053,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>37</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="5" t="s">
         <v>38</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="5" t="s">
         <v>39</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>2.9999999999999999E-307</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" s="5" t="s">
         <v>40</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>9.9999999999999998E-201</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" s="5" t="s">
         <v>41</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>5.0000000000000001E-101</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="5" t="s">
         <v>42</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>5.0000000000000001E-100</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" s="10" t="s">
         <v>43</v>
       </c>
@@ -2304,7 +2304,7 @@
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -2316,7 +2316,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
         <v>35</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55" s="5">
         <v>1</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>5.0000000000000001E-100</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56" s="5">
         <v>2</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>1E-100</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" s="5">
         <v>3</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>4.9999999999999999E-200</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58" s="5">
         <v>4</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>9.9999999999999998E-201</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" s="5">
         <v>5</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>5.0000000000000001E-307</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" s="5">
         <v>6</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>9.9999999999999991E-308</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" s="5">
         <v>7</v>
       </c>
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
         <v>44</v>
       </c>
@@ -2649,7 +2649,7 @@
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -2661,7 +2661,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66" s="7" t="s">
         <v>35</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67" s="5">
         <v>1</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B68" s="5">
         <v>2</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>9.9999999999999991E-308</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69" s="5">
         <v>3</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>5.0000000000000001E-307</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B70" s="5">
         <v>4</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>9.9999999999999998E-201</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B71" s="5">
         <v>5</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>4.9999999999999999E-200</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72" s="5">
         <v>6</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>1E-100</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B73" s="5">
         <v>7</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>5.0000000000000001E-100</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
         <v>45</v>
       </c>
@@ -2994,7 +2994,7 @@
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -3006,7 +3006,7 @@
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78" s="11" t="s">
         <v>46</v>
       </c>
@@ -3020,7 +3020,7 @@
       <c r="J78" s="11"/>
       <c r="K78" s="11"/>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79" s="7" t="s">
         <v>47</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80" s="5" t="s">
         <v>13</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B81" s="5" t="s">
         <v>14</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B82" s="5" t="s">
         <v>16</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B83" s="5" t="s">
         <v>17</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="s">
         <v>18</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="5" t="s">
         <v>19</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B86" s="5" t="s">
         <v>21</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="12" t="s">
         <v>48</v>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="J88" s="11"/>
       <c r="K88" s="11"/>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="7" t="s">
         <v>47</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="5" t="s">
         <v>13</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B91" s="5" t="s">
         <v>14</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B92" s="5" t="s">
         <v>16</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="5" t="s">
         <v>17</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="s">
         <v>18</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="5" t="s">
         <v>19</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B96" s="5" t="s">
         <v>21</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B99" s="10" t="s">
         <v>49</v>
       </c>
@@ -3686,7 +3686,7 @@
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -3698,7 +3698,7 @@
       <c r="J100" s="2"/>
       <c r="K100" s="2"/>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B101" s="11" t="s">
         <v>50</v>
       </c>
@@ -3712,7 +3712,7 @@
       <c r="J101" s="11"/>
       <c r="K101" s="11"/>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B102" s="7" t="s">
         <v>51</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B103" s="8">
         <v>1</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B104" s="8">
         <v>2</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B105" s="8">
         <v>3</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B106" s="8">
         <v>4</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B107" s="8">
         <v>5</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B108" s="8">
         <v>6</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B109" s="8">
         <v>7</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B110" s="8">
         <v>8</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B111" s="8">
         <v>9</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B112" s="8">
         <v>10</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B115" s="4" t="s">
         <v>63</v>
       </c>
@@ -3913,7 +3913,7 @@
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -3925,7 +3925,7 @@
       <c r="J116" s="2"/>
       <c r="K116" s="2"/>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B117" s="7" t="s">
         <v>64</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B118" s="3" t="s">
         <v>67</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B119" s="3" t="s">
         <v>69</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B120" s="3" t="s">
         <v>71</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B121" s="3" t="s">
         <v>73</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B122" s="3" t="s">
         <v>75</v>
       </c>
@@ -3996,7 +3996,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B123" s="3" t="s">
         <v>77</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B124" s="3" t="s">
         <v>79</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B125" s="3" t="s">
         <v>81</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B126" s="3" t="s">
         <v>83</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B127" s="3" t="s">
         <v>85</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B128" s="3" t="s">
         <v>87</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B129" s="3" t="s">
         <v>89</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B132" s="10" t="s">
         <v>91</v>
       </c>
@@ -4094,7 +4094,7 @@
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -4106,7 +4106,7 @@
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B134" s="7" t="s">
         <v>64</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B135" s="3" t="s">
         <v>92</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B136" s="3" t="s">
         <v>94</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B137" s="3" t="s">
         <v>96</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B138" s="3" t="s">
         <v>98</v>
       </c>
@@ -4165,7 +4165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B139" s="3" t="s">
         <v>100</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B140" s="3" t="s">
         <v>102</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B141" s="3" t="s">
         <v>104</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B142" s="3" t="s">
         <v>106</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B143" s="3" t="s">
         <v>108</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B144" s="3" t="s">
         <v>110</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B145" s="3" t="s">
         <v>112</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B146" s="3" t="s">
         <v>114</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B149" s="10" t="s">
         <v>0</v>
       </c>
@@ -4275,7 +4275,7 @@
       <c r="J149" s="4"/>
       <c r="K149" s="4"/>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B150" s="15" t="e">
         <v>#N/A</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B151" s="15" t="e">
         <v>#NUM!</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B152" s="15" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B153" s="15" t="e">
         <v>#VALUE!</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B154" s="16" t="s">
         <v>130</v>
       </c>
@@ -4315,7 +4315,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B155" s="15" t="s">
         <v>121</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B156" s="15" t="s">
         <v>123</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B157" s="15" t="s">
         <v>125</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B158" s="15" t="s">
         <v>31</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B159" s="15" t="s">
         <v>128</v>
       </c>
